--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Students/AdminApp_Students_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Students/AdminApp_Students_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="404">
   <si>
     <t>S.No.</t>
   </si>
@@ -329,49 +329,54 @@
     <t>TST_SLST_TC_13</t>
   </si>
   <si>
-    <t>Verify the "Who activated the code in my school?" checkbox can be toggled and re-queries the list</t>
+    <t>Verify the activation-code hint is shown when the "Who activated the code in my school?" checkbox is ticked</t>
   </si>
   <si>
     <t>#5 — Verify search with "who activated the code in my school?" checkbox</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Tick the "Who activated the code in my school?" checkbox.
-2. Wait for the list to settle.
-3. Observe the heading and rows.
-4. Untick the checkbox and observe again.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The checkbox toggles on and off cleanly and the list re-renders each time without error; "Load more ..." remains available.
-[ASSUMED] that ticking the box restricts the list to students who activated a code in this school. On FCN-CHZ-PDA the result set was IDENTICAL with the box ticked and unticked (26 students, same first five rows, 2026-08-22), so the filtering effect could not be demonstrated here.</t>
-  </si>
-  <si>
-    <t>Needs &lt;SCHOOL_WITH_MIXED_ACTIVATION&gt; — a school holding both students who activated a code and students who did not. Confirm the differentiating behaviour during Phase 1.</t>
+    <t xml:space="preserve">1. Observe the search box placeholder before ticking anything.
+2. Tick the "Who activated the code in my school?" checkbox.
+3. Observe the area directly below the checkbox, and the search box placeholder.
+4. Untick the checkbox and observe both again.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After step 2 a hint appears directly below the checkbox reading exactly: "A user activation code usually has 16 characters, both letters and numbers."
+The search box placeholder changes from "Search by first name, last name, email or username" to empty, showing the search now takes an activation code rather than a name.
+After step 4 the hint is removed from the page and the original placeholder is restored.
+The student list is EXPECTED TO STAY THE SAME throughout - the checkbox changes what the search box searches by; it does not filter the list on its own.</t>
+  </si>
+  <si>
+    <t>Corrected 2026-08-26, verified live. This case previously expected the checkbox to FILTER the list to students who had activated a code, and recorded the identical 26-student result on FCN-CHZ-PDA as an unproven [ASSUMED] needing a &lt;SCHOOL_WITH_MIXED_ACTIVATION&gt;. That premise was wrong: the checkbox is a search-mode switch, not a filter, so an unchanged list with an empty search box is CORRECT behaviour, not a gap - and no special school is needed. Note the copy says "16 characters, both letters and numbers", NOT "16 digits"; assert it verbatim. The activation-code search itself is exercised by TST_SLST_TC_14 (Blocked).</t>
   </si>
   <si>
     <t>TST_SLST_TC_14</t>
   </si>
   <si>
-    <t>Verify the activation checkbox and a search term can be applied together</t>
+    <t>Verify a student can be found by activation code when the "Who activated the code in my school?" checkbox is ticked</t>
+  </si>
+  <si>
+    <t>Logged in as school admin (testt1@mailsac.com) on Thor. School "3 July Test School 1" (key FCN-CHZ-PDA) opened from "My school accounts". Students tab is displayed. An activation code redeemed by a student in this school is known.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Tick "Who activated the code in my school?".
-2. Type a first name that matches a student who has NOT activated a code.
+2. Type an activation code into the search box (with the checkbox ticked, the search box searches by activation code - NOT by name).
 3. Click Search.</t>
   </si>
   <si>
-    <t>&lt;STUDENT_WITHOUT_ACTIVATED_CODE&gt;</t>
-  </si>
-  <si>
-    <t>[ASSUMED] The two conditions combine (AND): the named student is excluded because they have not activated a code, and the empty result is shown.</t>
-  </si>
-  <si>
-    <t>Blocked at design time on FCN-CHZ-PDA for the same reason as TST_SLST_TC_13 — the checkbox has no observable effect there, so the combination cannot be distinguished from search alone.</t>
+    <t>&lt;VALID_ACTIVATION_CODE&gt; - an activation code redeemed by a student in this school</t>
+  </si>
+  <si>
+    <t>[ASSUMED] The list is restricted to the student(s) who activated the supplied code.</t>
+  </si>
+  <si>
+    <t>Corrected 2026-08-26. This case previously had step 2 as "type a first name" and expected the checkbox to AND with a name search. That was wrong: the checkbox does not filter a name search - it changes what the search box searches by, from student name to activation code. The step and expected result now reflect that. Still [ASSUMED] - the behaviour cannot be observed on the current environment (see Comments).</t>
   </si>
   <si>
     <t>Blocked</t>
   </si>
   <si>
-    <t>Blocked at design time. The activation checkbox has no observable effect on 3 July Test School 1 (FCN-CHZ-PDA), so its combination with a search term cannot be distinguished from search alone. Unblocked by a school holding both students who activated a code and students who did not.</t>
+    <t>Blocked at design time. No activation code is currently available on the test environment, and a known application issue prevents this path being exercised, so the activation-code search cannot be validated. Do not automate this case for now. Unblocked by a school with a student who has redeemed a known activation code, once the application issue is resolved.</t>
   </si>
   <si>
     <t>TST_SLST_TC_15</t>
@@ -502,7 +507,7 @@
     <t>TST_SLST_TC_22</t>
   </si>
   <si>
-    <t>Verify Load more appends the remaining students to the list</t>
+    <t>Verify Load more appends the next page of 20 students without replacing the rows already shown</t>
   </si>
   <si>
     <t>#16 — Verify load more feature</t>
@@ -512,32 +517,39 @@
   </si>
   <si>
     <t xml:space="preserve">1. Count the rows on first load.
+2. Note the first and last student shown.
+3. Click "Load more ..." ONCE.
+4. Count the rows again.
+5. Confirm the students noted in step 2 are still present, in the same order.</t>
+  </si>
+  <si>
+    <t>The first page holds exactly 20 rows. After ONE click the list holds 20 + min(20, remaining) rows - i.e. 40 on a school with 40+ students, or fewer only when the school has fewer than 40 in total. The 20 rows already shown are retained in place, not replaced, and the sort order is preserved.</t>
+  </si>
+  <si>
+    <t>Corrected 2026-08-26. This previously read "after Load more the list holds every student in the school (26 at the time of capture)" and told automation to assert "list length equals the heading count". That is only true because FCN-CHZ-PDA held 26 students, so ONE click happened to exhaust it. Load more appends the NEXT 20, not the remainder - on an 85-student school one click gives 40, and the old assertion would fail against a healthy product. Assert the delta (+20, capped by what remains), never the heading total. Exhaustion is covered separately by TST_SLST_TC_23. Page size 20, verified live 2026-08-22 - same as the Classes tab.</t>
+  </si>
+  <si>
+    <t>TST_SLST_TC_23</t>
+  </si>
+  <si>
+    <t>Verify Load more disappears once every student has been loaded</t>
+  </si>
+  <si>
+    <t>Logged in as school admin (testt1@mailsac.com) on Thor. School "3 July Test School 1" (key FCN-CHZ-PDA) opened from "My school accounts". Students tab is displayed with the first page of 20 rows and "Load more ..." present.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Note the count in the heading "Students (N)".
 2. Click "Load more ...".
-3. Count the rows again.</t>
-  </si>
-  <si>
-    <t>The first page holds exactly 20 rows. After Load more the list holds every student in the school (26 at the time of capture) and the previously loaded rows are retained, not replaced.</t>
-  </si>
-  <si>
-    <t>Verified live 2026-08-22. Page size 20 — the same as the Classes tab. Do not assert the absolute total on this shared school; assert "20 before, list length equals the heading count after".</t>
-  </si>
-  <si>
-    <t>TST_SLST_TC_23</t>
-  </si>
-  <si>
-    <t>Verify Load more disappears once every student has been loaded</t>
-  </si>
-  <si>
-    <t>Logged in as school admin (testt1@mailsac.com) on Thor. School "3 July Test School 1" (key FCN-CHZ-PDA) opened from "My school accounts". Students tab is displayed. Load more has been clicked until all students are listed.</t>
-  </si>
-  <si>
-    <t>1. Look for the "Load more ..." link.</t>
-  </si>
-  <si>
-    <t>The link is REMOVED from the page — it is not left visible in a disabled state.</t>
-  </si>
-  <si>
-    <t>Verified live 2026-08-22. Automation must assert absence, not disabled-ness.</t>
+3. Wait for the new rows to render.
+4. REPEAT steps 2-3 while the "Load more ..." link is still present - do not assume a fixed number of clicks.
+5. When the link is gone, look for it on the page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each click appends the next page of 20 (the last click appending only what remains). Once the whole list is loaded, "Load more ..." is REMOVED from the page - it is not left visible in a disabled state.
+The number of clicks required is ceil(N / 20) - 1, where N is the heading count: e.g. 26 students = 1 click, 80 = 3 clicks, 85 = 4 clicks. A school with exactly 20 or fewer never shows the link at all.</t>
+  </si>
+  <si>
+    <t>Verified live 2026-08-22. Automation must assert absence, not disabled-ness, and must LOOP until the link disappears rather than clicking a fixed number of times. Note the trap: FCN-CHZ-PDA held 26 students at capture, so ONE click exhausted the list - a single-click implementation would pass there and break as soon as the school exceeds 40. The exhaustion loop was previously buried in this case Preconditions; it is now an explicit step. Related: TST_SLST_TC_22 covers the single-click append.</t>
   </si>
   <si>
     <t>TST_SLST_TC_24</t>
@@ -2372,28 +2384,28 @@
         <v>55</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2401,13 +2413,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>17</v>
@@ -2419,16 +2431,16 @@
         <v>19</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>24</v>
@@ -2445,13 +2457,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>17</v>
@@ -2463,13 +2475,13 @@
         <v>19</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>45</v>
@@ -2489,13 +2501,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>17</v>
@@ -2507,16 +2519,16 @@
         <v>19</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>24</v>
@@ -2533,13 +2545,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>48</v>
@@ -2551,16 +2563,16 @@
         <v>19</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>24</v>
@@ -2577,13 +2589,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>48</v>
@@ -2592,19 +2604,19 @@
         <v>55</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>24</v>
@@ -2621,13 +2633,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>17</v>
@@ -2639,16 +2651,16 @@
         <v>19</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>24</v>
@@ -2665,13 +2677,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>17</v>
@@ -2680,19 +2692,19 @@
         <v>41</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>24</v>
@@ -2709,13 +2721,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>17</v>
@@ -2724,19 +2736,19 @@
         <v>18</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>24</v>
@@ -2753,13 +2765,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>48</v>
@@ -2768,19 +2780,19 @@
         <v>41</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>24</v>
@@ -2797,13 +2809,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>48</v>
@@ -2815,13 +2827,13 @@
         <v>19</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>45</v>
@@ -2841,13 +2853,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>17</v>
@@ -2856,19 +2868,19 @@
         <v>41</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>24</v>
@@ -2885,13 +2897,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>17</v>
@@ -2903,16 +2915,16 @@
         <v>19</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>24</v>
@@ -2929,13 +2941,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>17</v>
@@ -2944,19 +2956,19 @@
         <v>41</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>24</v>
@@ -2973,13 +2985,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>17</v>
@@ -2988,16 +3000,16 @@
         <v>41</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>45</v>
@@ -3017,13 +3029,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>48</v>
@@ -3032,19 +3044,19 @@
         <v>55</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>24</v>
@@ -3061,13 +3073,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>62</v>
@@ -3079,16 +3091,16 @@
         <v>19</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>24</v>
@@ -3105,13 +3117,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>17</v>
@@ -3123,13 +3135,13 @@
         <v>19</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>45</v>
@@ -3149,13 +3161,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>17</v>
@@ -3167,25 +3179,25 @@
         <v>19</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="34" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3193,13 +3205,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>17</v>
@@ -3208,19 +3220,19 @@
         <v>18</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>24</v>
@@ -3237,13 +3249,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>62</v>
@@ -3252,19 +3264,19 @@
         <v>18</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>24</v>
@@ -3281,13 +3293,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>17</v>
@@ -3296,19 +3308,19 @@
         <v>18</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>24</v>
@@ -3325,13 +3337,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>48</v>
@@ -3340,19 +3352,19 @@
         <v>41</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>24</v>
@@ -3369,13 +3381,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>48</v>
@@ -3384,19 +3396,19 @@
         <v>41</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>24</v>
@@ -3413,13 +3425,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>62</v>
@@ -3428,19 +3440,19 @@
         <v>41</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>24</v>
@@ -3457,13 +3469,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>17</v>
@@ -3475,16 +3487,16 @@
         <v>19</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>24</v>
@@ -3501,13 +3513,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>48</v>
@@ -3516,19 +3528,19 @@
         <v>41</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>24</v>
@@ -3545,13 +3557,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>62</v>
@@ -3560,19 +3572,19 @@
         <v>18</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>24</v>
@@ -3589,13 +3601,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>17</v>
@@ -3604,19 +3616,19 @@
         <v>18</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>24</v>
@@ -3633,13 +3645,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>62</v>
@@ -3648,19 +3660,19 @@
         <v>18</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>24</v>
@@ -3677,13 +3689,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>17</v>
@@ -3695,16 +3707,16 @@
         <v>19</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>24</v>
@@ -3721,13 +3733,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>48</v>
@@ -3736,28 +3748,28 @@
         <v>41</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3765,13 +3777,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>48</v>
@@ -3783,16 +3795,16 @@
         <v>19</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>24</v>
@@ -3809,13 +3821,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>62</v>
@@ -3824,19 +3836,19 @@
         <v>41</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>24</v>
@@ -3853,13 +3865,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>17</v>
@@ -3868,19 +3880,19 @@
         <v>18</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>24</v>
@@ -3897,13 +3909,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>48</v>
@@ -3915,16 +3927,16 @@
         <v>19</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>24</v>
@@ -3941,13 +3953,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>17</v>
@@ -3956,19 +3968,19 @@
         <v>18</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>24</v>
@@ -3985,13 +3997,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>17</v>
@@ -4000,19 +4012,19 @@
         <v>18</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>24</v>
@@ -4029,13 +4041,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>17</v>
@@ -4044,19 +4056,19 @@
         <v>18</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>24</v>
@@ -4073,13 +4085,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>17</v>
@@ -4088,19 +4100,19 @@
         <v>41</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>24</v>
@@ -4117,13 +4129,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>17</v>
@@ -4135,16 +4147,16 @@
         <v>19</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>24</v>
@@ -4161,13 +4173,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>17</v>
@@ -4176,19 +4188,19 @@
         <v>41</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>24</v>
@@ -4205,13 +4217,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>48</v>
@@ -4220,19 +4232,19 @@
         <v>41</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>24</v>
@@ -4249,13 +4261,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>62</v>
@@ -4264,19 +4276,19 @@
         <v>18</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>24</v>
@@ -4293,13 +4305,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>62</v>
@@ -4308,19 +4320,19 @@
         <v>41</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>24</v>
@@ -4337,13 +4349,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>62</v>
@@ -4352,19 +4364,19 @@
         <v>41</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>24</v>
@@ -4387,6 +4399,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Students/AdminApp_Students_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Students/AdminApp_Students_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="404">
   <si>
     <t>S.No.</t>
   </si>
@@ -90,7 +90,7 @@
     <t/>
   </si>
   <si>
-    <t>Not Run</t>
+    <t>Pass</t>
   </si>
   <si>
     <t>TST_SLST_TC_2</t>
@@ -212,20 +212,21 @@
     <t>Negative</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Type "zzz_no_such_student" into the search box.
+    <t xml:space="preserve">1. Type "zzz-no-such-student-9999" into the search box.
 2. Click Search.
 3. Observe the area below the toolbar.
 4. Open the browser console.</t>
   </si>
   <si>
-    <t>Non-matching term: zzz_no_such_student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An explicit empty-state message should be shown, echoing the term — the Classes tab's equivalent reads "No classes that match your search &lt;term&gt;".
-ACTUAL (defect, observed 2026-08-22): NOTHING is rendered. The whole table, including the sort header row, is removed and no message replaces it — the user sees a blank area. The console logs "ERROR TypeError: Cannot read properties of undefined (reading 'length') at o.search" from the admin bundle, so the empty state appears to be failing to render rather than being absent by design.</t>
-  </si>
-  <si>
-    <t>DEFECT — raise. Evidence: screenshot students-no-results.png + console trace, Thor 2026-08-22. Expected copy is [ASSUMED] (no verified string exists because the state never renders).</t>
+    <t>Non-matching term: zzz-no-such-student-9999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The table (including the sort header row) is removed and an explicit empty-state message replaces it, echoing the search term verbatim in bold:
+"This school has no students that match your search &lt;term&gt;. Please check the spelling or try a different search term"
+The search banner still reads "Students / Showing search results for &lt;term&gt;. / Clear", the Clear link remains available, and NO console error is logged.</t>
+  </si>
+  <si>
+    <t>DEFECT NOW FIXED — verified live on Thor 2026-08-28. Between 2026-08-22 and 2026-08-28 the product was corrected. Originally raised as a defect: nothing rendered at all (table removed, no message) and the console threw "TypeError: Cannot read properties of undefined (reading 'length') at o.search" — see students-no-results.png, which is now HISTORIC evidence and no longer reflects current behaviour. Re-verified 2026-08-28: message renders correctly, zero console errors. Automation asserts the FIXED behaviour; do not re-introduce the defect expectation. Empty-state node: div.no-records &gt; p.mb-0.</t>
   </si>
   <si>
     <t>TST_SLST_TC_4</t>
@@ -335,43 +336,46 @@
     <t>#5 — Verify search with "who activated the code in my school?" checkbox</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Tick the "Who activated the code in my school?" checkbox.
-2. Wait for the list to settle.
-3. Observe the heading and rows.
-4. Untick the checkbox and observe again.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The checkbox toggles on and off cleanly and the list re-renders each time without error; "Load more ..." remains available.
-[ASSUMED] that ticking the box restricts the list to students who activated a code in this school. On FCN-CHZ-PDA the result set was IDENTICAL with the box ticked and unticked (26 students, same first five rows, 2026-08-22), so the filtering effect could not be demonstrated here.</t>
-  </si>
-  <si>
-    <t>Needs &lt;SCHOOL_WITH_MIXED_ACTIVATION&gt; — a school holding both students who activated a code and students who did not. Confirm the differentiating behaviour during Phase 1.</t>
+    <t xml:space="preserve">1. Note the heading "Students (N)", the number of listed rows and the first row's name.
+2. Tick the "Who activated the code in my school?" checkbox.
+3. Wait for the list to settle.
+4. Observe the area directly beneath the checkbox, and the heading and rows.
+5. Untick the checkbox and observe again.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The checkbox is a SEARCH-MODE SWITCH, not a list filter. On ticking, two helper lines appear directly beneath the checkbox, verbatim:
+"This search can take up to 1 minute to complete, please be patient."
+"A user activation code usually has 16 characters, both letters and numbers."
+The search box now expects a 16-character activation code instead of a name/email/username. The list itself is UNCHANGED — the heading still reads "Students (N)" with the same N, the same rows are listed in the same order, and "Load more ..." remains available. On unticking, both helper lines are removed from the DOM and the search box reverts to name/email/username matching.</t>
+  </si>
+  <si>
+    <t>Expected result CORRECTED and verified live on Thor 2026-08-28. The original [ASSUMED] expectation — that ticking filters the list to students who activated a code — was WRONG; the checkbox does not filter at all. The DOM confirms it: the input carries name="activation-code-search" (id="activationCheckbox", qid="aLearner-17"). The identical 26-row result seen on 2026-08-22 was correct behaviour, not a missing filter, so &lt;SCHOOL_WITH_MIXED_ACTIVATION&gt; is NOT required — that note is withdrawn. Fully automatable on FCN-CHZ-PDA; needs no activation code.</t>
   </si>
   <si>
     <t>TST_SLST_TC_14</t>
   </si>
   <si>
-    <t>Verify the activation checkbox and a search term can be applied together</t>
+    <t>Verify searching by a redeemed activation code returns the student who activated it</t>
   </si>
   <si>
     <t xml:space="preserve">1. Tick "Who activated the code in my school?".
-2. Type a first name that matches a student who has NOT activated a code.
-3. Click Search.</t>
-  </si>
-  <si>
-    <t>&lt;STUDENT_WITHOUT_ACTIVATED_CODE&gt;</t>
-  </si>
-  <si>
-    <t>[ASSUMED] The two conditions combine (AND): the named student is excluded because they have not activated a code, and the empty result is shown.</t>
-  </si>
-  <si>
-    <t>Blocked at design time on FCN-CHZ-PDA for the same reason as TST_SLST_TC_13 — the checkbox has no observable effect there, so the combination cannot be distinguished from search alone.</t>
+2. Type a 16-character activation code that has already been redeemed by a known student in this school.
+3. Click Search (allow up to 1 minute — the helper text warns of this).</t>
+  </si>
+  <si>
+    <t>&lt;REDEEMED_ACTIVATION_CODE&gt; + the name/email of the student who redeemed it</t>
+  </si>
+  <si>
+    <t>The list narrows to the single student who redeemed that code, matching the expected name and email/username. The search banner reads "Students / Showing search results for &lt;code&gt;. / Clear".</t>
+  </si>
+  <si>
+    <t>Rewritten 2026-08-28. The original scenario — "activation checkbox AND a search term combine as an AND filter" — was based on a misreading of the checkbox; it is a search-MODE switch, so there is no combination to test (see TST_SLST_TC_13). This case now covers the checkbox's actual purpose: searching BY activation code. Still Blocked, but for a different and narrower reason.</t>
   </si>
   <si>
     <t>Blocked</t>
   </si>
   <si>
-    <t>Blocked at design time. The activation checkbox has no observable effect on 3 July Test School 1 (FCN-CHZ-PDA), so its combination with a search term cannot be distinguished from search alone. Unblocked by a school holding both students who activated a code and students who did not.</t>
+    <t>Blocked 2026-08-28 on TEST DATA, not on school fixtures. Needs a 16-character activation code already redeemed by a known student, plus that student's identity. The environment that issues activation codes is down, so no code can be obtained. The earlier block reason — "the checkbox has no observable effect on FCN-CHZ-PDA" — was incorrect and is withdrawn: the checkbox is not a filter, so identical ticked/unticked results were correct behaviour. &lt;SCHOOL_WITH_MIXED_ACTIVATION&gt; is NOT required. Unblocked by: one redeemed activation code + its student.</t>
   </si>
   <si>
     <t>TST_SLST_TC_15</t>
@@ -455,10 +459,10 @@
 2. Read the sort indicators.</t>
   </si>
   <si>
-    <t>[ASSUMED] The list returns to the default First name ascending sort — sorting does not persist, unlike the Classes tab's search and filter which persist server-side per user.</t>
-  </si>
-  <si>
-    <t>Not run live 2026-08-22. The Classes tab behaves this way (admin-shared.md §A4); confirm for Students during Phase 1.</t>
+    <t>The list returns to the default First name ascending sort — sorting does NOT persist across a reload, unlike the Classes tab's search and filter which persist server-side per user. The sort-status indicator returns to #sortStatus-learner-first_name reading "sorted ascending".</t>
+  </si>
+  <si>
+    <t>CONFIRMED live on Thor 2026-08-28 — the [ASSUMED] tag is removed. Sorted by Last name descending, reloaded, and the list came back sorted by First name ascending with the original first row restored. Matches the Classes tab (admin-shared.md §A4).</t>
   </si>
   <si>
     <t>TST_SLST_TC_20</t>
@@ -581,6 +585,9 @@
   </si>
   <si>
     <t>CREATES REAL DATA on a shared school, and the count on FCN-CHZ-PDA is moved by other teams during a session — so a strict N+1 assertion is unsafe here. Prefer asserting that the specific new student is findable by search. Not run 2026-08-22.</t>
+  </si>
+  <si>
+    <t>Not Run</t>
   </si>
   <si>
     <t>TST_SPRF_TC_1</t>
@@ -2366,10 +2373,10 @@
         <v>100</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>19</v>
@@ -2874,7 +2881,7 @@
         <v>24</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>24</v>
@@ -2885,13 +2892,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>17</v>
@@ -2903,22 +2910,22 @@
         <v>19</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>24</v>
@@ -2929,13 +2936,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>17</v>
@@ -2944,25 +2951,25 @@
         <v>41</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>24</v>
@@ -2973,13 +2980,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>17</v>
@@ -2988,16 +2995,16 @@
         <v>41</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>45</v>
@@ -3006,7 +3013,7 @@
         <v>24</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>24</v>
@@ -3017,13 +3024,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>48</v>
@@ -3032,25 +3039,25 @@
         <v>55</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>24</v>
@@ -3061,13 +3068,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>62</v>
@@ -3079,22 +3086,22 @@
         <v>19</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>24</v>
@@ -3105,13 +3112,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>17</v>
@@ -3123,13 +3130,13 @@
         <v>19</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>45</v>
@@ -3138,7 +3145,7 @@
         <v>24</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>24</v>
@@ -3149,13 +3156,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>17</v>
@@ -3167,16 +3174,16 @@
         <v>19</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>24</v>
@@ -3185,7 +3192,7 @@
         <v>110</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="34" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3193,13 +3200,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>17</v>
@@ -3208,25 +3215,25 @@
         <v>18</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>24</v>
@@ -3237,13 +3244,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>62</v>
@@ -3252,25 +3259,25 @@
         <v>18</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>24</v>
@@ -3281,13 +3288,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>17</v>
@@ -3296,25 +3303,25 @@
         <v>18</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>24</v>
@@ -3325,13 +3332,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>48</v>
@@ -3340,25 +3347,25 @@
         <v>41</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>24</v>
@@ -3369,13 +3376,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>48</v>
@@ -3384,25 +3391,25 @@
         <v>41</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>24</v>
@@ -3413,13 +3420,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>62</v>
@@ -3428,25 +3435,25 @@
         <v>41</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>24</v>
@@ -3457,13 +3464,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>17</v>
@@ -3475,22 +3482,22 @@
         <v>19</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>24</v>
@@ -3501,13 +3508,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>48</v>
@@ -3516,25 +3523,25 @@
         <v>41</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>24</v>
@@ -3545,13 +3552,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>62</v>
@@ -3560,25 +3567,25 @@
         <v>18</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>24</v>
@@ -3589,13 +3596,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>17</v>
@@ -3604,25 +3611,25 @@
         <v>18</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>24</v>
@@ -3633,13 +3640,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>62</v>
@@ -3648,25 +3655,25 @@
         <v>18</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>24</v>
@@ -3677,13 +3684,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>17</v>
@@ -3695,22 +3702,22 @@
         <v>19</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>24</v>
@@ -3721,13 +3728,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>48</v>
@@ -3736,19 +3743,19 @@
         <v>41</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>24</v>
@@ -3757,7 +3764,7 @@
         <v>110</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3765,13 +3772,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>48</v>
@@ -3783,22 +3790,22 @@
         <v>19</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>24</v>
@@ -3809,13 +3816,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>62</v>
@@ -3824,25 +3831,25 @@
         <v>41</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>24</v>
@@ -3853,13 +3860,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>17</v>
@@ -3868,25 +3875,25 @@
         <v>18</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>24</v>
@@ -3897,13 +3904,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>48</v>
@@ -3915,22 +3922,22 @@
         <v>19</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>24</v>
@@ -3941,13 +3948,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>17</v>
@@ -3956,25 +3963,25 @@
         <v>18</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>24</v>
@@ -3985,13 +3992,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>17</v>
@@ -4000,25 +4007,25 @@
         <v>18</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>24</v>
@@ -4029,13 +4036,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>17</v>
@@ -4044,25 +4051,25 @@
         <v>18</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>24</v>
@@ -4073,13 +4080,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>17</v>
@@ -4088,25 +4095,25 @@
         <v>41</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>24</v>
@@ -4117,13 +4124,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>17</v>
@@ -4135,22 +4142,22 @@
         <v>19</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N55" s="2" t="s">
         <v>24</v>
@@ -4161,13 +4168,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>17</v>
@@ -4176,25 +4183,25 @@
         <v>41</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N56" s="2" t="s">
         <v>24</v>
@@ -4205,13 +4212,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>48</v>
@@ -4220,25 +4227,25 @@
         <v>41</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>24</v>
@@ -4249,13 +4256,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>62</v>
@@ -4264,25 +4271,25 @@
         <v>18</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>24</v>
@@ -4293,13 +4300,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>62</v>
@@ -4308,25 +4315,25 @@
         <v>41</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>24</v>
@@ -4337,13 +4344,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>62</v>
@@ -4352,25 +4359,25 @@
         <v>41</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="N60" s="2" t="s">
         <v>24</v>
@@ -4387,6 +4394,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Students/AdminApp_Students_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Students/AdminApp_Students_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="476">
   <si>
     <t>S.No.</t>
   </si>
@@ -84,7 +84,7 @@
     <t>URL is /admin/admin/org_perf_testschool_1/learner. Heading reads "Students (N)". The page shows: search box with placeholder "Search by first name, last name, email or username", a Search button, the checkbox "Who activated the code in my school?", a "Manage students" dropdown, a select-all checkbox with "0 Selected", a disabled "Remove from school account" button, a "User guide" toggle, and a table with sort headers Last name / First name / Email address or Username.</t>
   </si>
   <si>
-    <t>Added by the designer — the source list has no explicit tab-load scenario, but every other case depends on this state. N moves on this shared school; never assert an absolute count.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Added by the designer — the source list has no explicit tab-load scenario, but every other case depends on this state. N moves on this shared school; never assert an absolute count.</t>
   </si>
   <si>
     <t/>
@@ -134,7 +134,7 @@
     <t>After step 3 the heading still reads "Students (N)" and the full first page of 20 rows is still listed — search is submit-driven, not live. Only after step 4 does the list narrow to one row.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-22 (heading "Students (26)", 20 rows, unchanged after typing). Same behaviour as the Classes tab.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-22 (heading "Students (26)", 20 rows, unchanged after typing). Same behaviour as the Classes tab.</t>
   </si>
   <si>
     <t>TST_SLST_TC_10</t>
@@ -156,7 +156,7 @@
     <t>The banner is replaced by the "Students (N)" count heading, the search box is emptied, the first page of 20 rows is listed again and "Load more ..." reappears.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-22.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-22.</t>
   </si>
   <si>
     <t>TST_SLST_TC_3</t>
@@ -200,7 +200,7 @@
     <t>All students are returned (first page of 20 rows). The search banner is shown but with no term between "Showing search results for" and the full stop — i.e. the term is trimmed away yet the banner state is still entered.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-22. Arguably the banner should not appear at all for an empty term — raise as a minor UX observation, not a functional failure.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-22. Arguably the banner should not appear at all for an empty term — raise as a minor UX observation, not a functional failure.</t>
   </si>
   <si>
     <t>TST_SLST_TC_12</t>
@@ -246,6 +246,9 @@
   </si>
   <si>
     <t>Exactly one row is listed — Last name "budhiraja", First name "niharika", Email "learner34@mailsac.com". Banner reads "Showing search results for budhiraja."</t>
+  </si>
+  <si>
+    <t>Verified live 2026-08-22.</t>
   </si>
   <si>
     <t>TST_SLST_TC_5</t>
@@ -443,7 +446,7 @@
     <t>Upper-case names sort before lower-case ones — Garg, Learner, Perf Test, S, … then budhiraja, kr, learner, student, test, us. An A-Z expectation that ignores case (localeCompare) will NOT match this product.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-22. Same collation rule already recorded for the Classes tab in admin-shared.md §A4.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-22. Same collation rule already recorded for the Classes tab in admin-shared.md §A4.</t>
   </si>
   <si>
     <t>TST_SLST_TC_19</t>
@@ -462,7 +465,7 @@
     <t>The list returns to the default First name ascending sort — sorting does NOT persist across a reload, unlike the Classes tab's search and filter which persist server-side per user. The sort-status indicator returns to #sortStatus-learner-first_name reading "sorted ascending".</t>
   </si>
   <si>
-    <t>CONFIRMED live on Thor 2026-08-28 — the [ASSUMED] tag is removed. Sorted by Last name descending, reloaded, and the list came back sorted by First name ascending with the original first row restored. Matches the Classes tab (admin-shared.md §A4).</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. CONFIRMED live on Thor 2026-08-28 — the [ASSUMED] tag is removed. Sorted by Last name descending, reloaded, and the list came back sorted by First name ascending with the original first row restored. Matches the Classes tab (admin-shared.md §A4).</t>
   </si>
   <si>
     <t>TST_SLST_TC_20</t>
@@ -631,7 +634,7 @@
     <t>Components are grouped under their umbrella name and each shows exactly one of three states: "Code activated" with "Activated: &lt;date&gt;" and "Expires: &lt;date&gt;"; "Code not activated" with no dates; or "Code expired" with "Activated: &lt;date&gt;" and "Expires: &lt;date&gt;" in the past.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-22. “Code expired” was seen only on this account — a fixture worth keeping. The “(N)” in “Course materials (N)” counts UMBRELLAS, not components.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-22. “Code expired” was seen only on this account — a fixture worth keeping. The “(N)” in “Course materials (N)” counts UMBRELLAS, not components.</t>
   </si>
   <si>
     <t>TST_SPRF_TC_5</t>
@@ -664,7 +667,7 @@
     <t>The profile page loads normally. This differs from the Classes tab, where deep-linking to /admin/admin/org_&lt;slug&gt;/class returns /dashboard/error unless the school card was clicked first.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-22, within a session where the school context had already been set. [ASSUMED] for a cold session with no prior school selection — worth confirming, since the Classes-tab rule suggests it may fail.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-22, within a session where the school context had already been set. [ASSUMED] for a cold session with no prior school selection — worth confirming, since the Classes-tab rule suggests it may fail.</t>
   </si>
   <si>
     <t>TST_SPRF_TC_7</t>
@@ -686,7 +689,7 @@
 ACTUAL (defect, observed 2026-08-22): the URL collapses to /class/ and the page shows an INFINITE SPINNER forever with no message and no way back other than the browser. The network log shows GET /class/apigateway/org_perf_testschool_1/getUserDetailWithClasses?...&amp;uuid=&lt;uuid&gt;&amp;extUserId=&lt;id&gt; returning HTTP 500.</t>
   </si>
   <si>
-    <t>DEFECT — raise. Two faults in one: the 500 itself (student-specific: other profiles on the same school load fine) and the missing client-side error handling for it. Evidence: screenshot profile-blank.png + console/network trace, Thor 2026-08-22.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. DEFECT — raise. Two faults in one: the 500 itself (student-specific: other profiles on the same school load fine) and the missing client-side error handling for it. Evidence: screenshot profile-blank.png + console/network trace, Thor 2026-08-22.</t>
   </si>
   <si>
     <t>TST_SPRF_TC_2</t>
@@ -843,7 +846,7 @@
     <t>A confirmation dialog is raised reading, verbatim: "Save changes?" / "Changes will be lost if you don’t save them" with "Cancel" and "Yes" buttons.</t>
   </si>
   <si>
-    <t>Copy captured free from the pre-rendered DOM 2026-08-22 (admin-shared.md §A6 trick) — the dialog was never triggered, but its text is verified. Which of Cancel/Yes discards versus saves is [ASSUMED] and must be confirmed.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Copy captured free from the pre-rendered DOM 2026-08-22 (admin-shared.md §A6 trick) — the dialog was never triggered, but its text is verified. Which of Cancel/Yes discards versus saves is [ASSUMED] and must be confirmed.</t>
   </si>
   <si>
     <t>TST_SPRF_TC_12</t>
@@ -1026,7 +1029,7 @@
     <t>The removal is refused and a dialog reads, verbatim: "You can only remove 50 students at one time" / "Please uncheck some students to continue", with a single "Close" action.</t>
   </si>
   <si>
-    <t>BLOCKED at design time on FCN-CHZ-PDA — the school holds 26 students, so 51 cannot be selected. The modal copy is nevertheless verified word for word from the pre-rendered DOM (2026-08-22), so this case is short work once a school with 51+ students exists. Unblocked by &lt;SCHOOL_WITH_51_PLUS_STUDENTS&gt;.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. BLOCKED at design time on FCN-CHZ-PDA — the school holds 26 students, so 51 cannot be selected. The modal copy is nevertheless verified word for word from the pre-rendered DOM (2026-08-22), so this case is short work once a school with 51+ students exists. Unblocked by &lt;SCHOOL_WITH_51_PLUS_STUDENTS&gt;.</t>
   </si>
   <si>
     <t>Blocked at design time. The 50-student removal cap needs 51+ students selected; FCN-CHZ-PDA holds 26. Modal copy is already verified word for word from the pre-rendered DOM, so this is short work once a larger school exists.</t>
@@ -1044,7 +1047,7 @@
     <t>The counter reads "0 Selected" and the "Remove from school account" button is disabled.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-22 — natively disabled.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-22 — natively disabled.</t>
   </si>
   <si>
     <t>TST_SPRF_TC_22</t>
@@ -1296,7 +1299,7 @@
 ACTUAL (defect, observed 2026-08-22): the dialog body renders three RAW UNTRANSLATED KEYS instead of text — "ADMIN.LEARNER.BULK_ACTIVATION.SUCCESS_MODAL_INFO_1", "...SUCCESS_MODAL_INFO_2" and "...SUCCESS_MODAL_INFO_3" — above a "Back to dashboard" button.</t>
   </si>
   <si>
-    <t>DEFECT — raise. Captured WITHOUT running a bulk activation, by reading the pre-rendered dialog in the DOM (admin-shared.md §A6). This is a user-visible failure waiting for the first successful bulk activation. The same page also holds "An unexpected error occured." (sic — “occured”) in its Form-not-uploaded dialog.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. DEFECT — raise. Captured WITHOUT running a bulk activation, by reading the pre-rendered dialog in the DOM (admin-shared.md §A6). This is a user-visible failure waiting for the first successful bulk activation. The same page also holds "An unexpected error occured." (sic — “occured”) in its Form-not-uploaded dialog.</t>
   </si>
   <si>
     <t>TST_SBLK_TC_10</t>
@@ -1312,7 +1315,7 @@
 ACTUAL (defect, observed 2026-08-22): the screen-reader-only label contains the raw key "ADMIN.LEARNER.BULK_ACTIVATION.SELECT_STUDENT", so a screen-reader user hears the translation key. The key is not visible on screen, which is why it has gone unnoticed.</t>
   </si>
   <si>
-    <t>DEFECT (accessibility) — raise alongside TST_SBLK_TC_9; same missing translation bundle. A third instance, "SCREEN_READER.PROCESSING_MESSAGE", appears on the individual activation page (TST_SPRF_TC_16), so this looks like one systemic gap rather than three separate typos.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. DEFECT (accessibility) — raise alongside TST_SBLK_TC_9; same missing translation bundle. A third instance, "SCREEN_READER.PROCESSING_MESSAGE", appears on the individual activation page (TST_SPRF_TC_16), so this looks like one systemic gap rather than three separate typos.</t>
   </si>
   <si>
     <t>TST_SBLK_TC_12</t>
@@ -1331,7 +1334,220 @@
     <t>The upload is refused and a dialog headed "Sorry, your file could not be uploaded" is shown, ending "If that doesn’t work, email our Customer Services team at ptsupport@cambridge.org". [ASSUMED for the specific reason line, which is populated per failure type.]</t>
   </si>
   <si>
-    <t>Dialog shell captured from the pre-rendered DOM 2026-08-22. The equivalent dialog on the adult CSV page enforces a 200-record maximum with its own wording (see product-knowledge/ExperienceApp.md); whether bulk activation shares that limit is unknown.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Dialog shell captured from the pre-rendered DOM 2026-08-22. The equivalent dialog on the adult CSV page enforces a 200-record maximum with its own wording (see product-knowledge/ExperienceApp.md); whether bulk activation shares that limit is unknown.</t>
+  </si>
+  <si>
+    <t>TST_SLST_TC_26</t>
+  </si>
+  <si>
+    <t>Verify a student whose name contains special characters is returned by a name search</t>
+  </si>
+  <si>
+    <t>#1 - Verify search by first name</t>
+  </si>
+  <si>
+    <t>On the Students tab of a school containing a student whose first or last name contains special characters.</t>
+  </si>
+  <si>
+    <t>1. Enter the name containing special characters in the search box. 2. Click Search. 3. Read the returned row(s) and the rendered name.</t>
+  </si>
+  <si>
+    <t>First name !^(+)s95 or &amp;FName - names present on the shared school per the other team's sheet. Confirm live before running.</t>
+  </si>
+  <si>
+    <t>The matching student is returned. The term is treated as literal text rather than interpreted, and the name is rendered correctly in the result row - not HTML-escaped, truncated or corrupted. [ASSUMED]</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_STU_001, which lists special-character names as fixtures. We already cover special characters in the email field (TST_SLST_TC_7) but never in a name field. SLST is already automated, so this is cheap to add. Read-only - no data created.</t>
+  </si>
+  <si>
+    <t>TST_SLST_TC_27</t>
+  </si>
+  <si>
+    <t>Verify a partial username returns every account whose username contains the term</t>
+  </si>
+  <si>
+    <t>#4 - Verify search by username</t>
+  </si>
+  <si>
+    <t>On the Students tab, with two or more accounts whose usernames share a common substring.</t>
+  </si>
+  <si>
+    <t>1. Enter a substring shared by several usernames (not a whole username). 2. Click Search. 3. Read the returned rows.</t>
+  </si>
+  <si>
+    <t>Username fragment &lt;SHARED_USERNAME_SUBSTRING&gt; - e.g. the common prefix of s95child0001-style accounts.</t>
+  </si>
+  <si>
+    <t>Every account whose username contains the term is returned, not only an exact match. [ASSUMED]</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_STU_004, whose step 2 searches a partial username. Our TST_SLST_TC_8 searches a full child username only. We already prove partial matching for first name (TST_SLST_TC_3), so username was the one identifier left unverified. Read-only.</t>
+  </si>
+  <si>
+    <t>TST_SLST_TC_28</t>
+  </si>
+  <si>
+    <t>Verify a never-activated code returns a clear no-result state in the activation-code search</t>
+  </si>
+  <si>
+    <t>#5 - Verify search using who activated the code in my school checkbox</t>
+  </si>
+  <si>
+    <t>On the Students tab with the "Who activated the code in my school?" checkbox ticked.</t>
+  </si>
+  <si>
+    <t>1. Tick Who activated the code in my school?. 2. Enter a well-formed 16-character code that has never been activated in this school. 3. Click Search. 4. Wait for the query to settle (the code search can take up to ~1 minute).</t>
+  </si>
+  <si>
+    <t>A syntactically valid but unredeemed 16-character code, e.g. AAAA-BBBB-CCCC-DDDD.</t>
+  </si>
+  <si>
+    <t>A clear no-result / empty state is shown, with no error and no stale results left from the previous query. [ASSUMED] - exact copy not captured.</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_STU_005, step 2. Our TST_SLST_TC_13 only toggles the checkbox and TST_SLST_TC_14 (Blocked, needs a known redeemed code) covers the success path, so the failure path was entirely unverified. This case is cheaper than TC_14 and can run today - it needs no seeded redemption. Read-only.</t>
+  </si>
+  <si>
+    <t>TST_SPRF_TC_23</t>
+  </si>
+  <si>
+    <t>Verify a learner can sign in with the password an administrator has just set</t>
+  </si>
+  <si>
+    <t>#11 - Verify Change password: View Profile &gt; Manage account &gt; Edit Account details</t>
+  </si>
+  <si>
+    <t>A disposable learner account exists whose credentials the tester controls and whose current password is known.</t>
+  </si>
+  <si>
+    <t>1. As admin, open the learner's profile &gt; Manage learner profile &gt; Password. 2. Set a new policy-compliant password and click Update. 3. Sign out. 4. Sign in as the learner with the new password. 5. Sign out and attempt to sign in with the old password.</t>
+  </si>
+  <si>
+    <t>Disposable learner &lt;DISPOSABLE_STUDENT_ACCOUNT&gt;; new password meeting the policy (min 8 characters, at least one letter and one number/special).</t>
+  </si>
+  <si>
+    <t>Sign-in with the new password succeeds and the learner reaches their dashboard. Sign-in with the old password is rejected. [ASSUMED]</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_STU_010, whose expected result is "login with the new password succeeds". Our TST_SPRF_TC_8 stops at the form accepting the update - which a change that was acknowledged but never persisted would also satisfy. Mutates a real account: use a disposable learner, never a shared fixture, and place it in a data-mutating suite.</t>
+  </si>
+  <si>
+    <t>TST_SBLK_TC_13</t>
+  </si>
+  <si>
+    <t>Verify a duplicate username is flagged on its own row during bulk account creation</t>
+  </si>
+  <si>
+    <t>#17 - Verify Bulk feature &gt; Add new students to classes children</t>
+  </si>
+  <si>
+    <t>On "Create new accounts for children" via Manage students &gt; Add new students to classes &gt; Children.</t>
+  </si>
+  <si>
+    <t>1. Fill one valid child row. 2. Fill a second row re-using the same username. 3. Read both rows and the submit button. 4. Repeat via the CSV path with the same duplicate pair.</t>
+  </si>
+  <si>
+    <t>Two child rows sharing one username; the rest of the fields valid.</t>
+  </si>
+  <si>
+    <t>The offending row is flagged (no green tick) with an error naming the username field, the valid row is unaffected, and Create N account(s) stays unavailable while any row is invalid. Behaviour is the same for the manual grid and the CSV upload. [ASSUMED]</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_STU_016_N1. Our SBLK negatives cover only the CSV-level rejection (TST_SBLK_TC_12) and two UI defects (TC_9 raw i18n keys, TC_10 checkbox label) - row-level validation was untested. This is the guard that stops bad accounts being created in bulk. Side-effect free provided the form is never submitted.</t>
+  </si>
+  <si>
+    <t>TST_SBLK_TC_14</t>
+  </si>
+  <si>
+    <t>Verify a rule-violating username or password is flagged on its own row during bulk account creation</t>
+  </si>
+  <si>
+    <t>#18 - Verify Bulk feature &gt; Add new students to classes adult with username</t>
+  </si>
+  <si>
+    <t>On "Create adult student accounts" via Manage students &gt; Add new students to classes &gt; Adults.</t>
+  </si>
+  <si>
+    <t>1. Fill one valid adult row. 2. Fill a second row with a username and a password that violate the documented rules. 3. Read both rows, the per-field messages and the submit button. 4. Repeat via the CSV path.</t>
+  </si>
+  <si>
+    <t>One valid adult row; one row with a rule-violating username and a rule-violating password.</t>
+  </si>
+  <si>
+    <t>The offending row is flagged (no green tick), the message identifies which field is wrong, the valid row is unaffected, and the submit control stays unavailable while any row is invalid. [ASSUMED] - the username and password rules must be read from the form's own help text before this case is finalised.</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_STU_017_N1. Companion to TST_SBLK_TC_13 on the adult path. Capture the stated rules verbatim on the first live pass - inventing them would breach golden rule 2. Side-effect free provided the form is never submitted.</t>
+  </si>
+  <si>
+    <t>TST_SBLK_TC_15</t>
+  </si>
+  <si>
+    <t>Verify an invalid code in a bulk activation is reported without blocking the valid rows</t>
+  </si>
+  <si>
+    <t>#21 - Verify Bulk feature &gt; Activate course material</t>
+  </si>
+  <si>
+    <t>On "Activate codes for students in your school" via Manage students &gt; Activate course materials.</t>
+  </si>
+  <si>
+    <t>1. Fill a batch mixing rows with valid unused codes and at least one already-used or invalid code. 2. Submit Activate N code(s). 3. Read the job outcome and, once processed, the affected learner profiles.</t>
+  </si>
+  <si>
+    <t>Valid unused 16-character codes plus one already-used/invalid code.</t>
+  </si>
+  <si>
+    <t>Only the bad row is flagged or reported in the job outcome; the valid rows still activate and their learners show "Code activated". A single bad row does not fail the whole batch. [ASSUMED]</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_STU_020_N1. Our TST_SBLK_TC_12 rejects an unprocessable CSV outright - the all-or-nothing path; this is the partial-failure path, which is where async bulk jobs typically break. Creates real data (consumes activation codes) - data-mutating suite only, and the codes cannot be reused.</t>
+  </si>
+  <si>
+    <t>TST_SBLK_TC_16</t>
+  </si>
+  <si>
+    <t>Verify the administrator receives an email report for an asynchronous bulk job</t>
+  </si>
+  <si>
+    <t>An administrator account whose mailbox the tester can read (e.g. a mailsac-style address). A bulk job has been submitted and its Request ID noted.</t>
+  </si>
+  <si>
+    <t>1. Submit a bulk job and record the Request ID and row count from the confirmation screen. 2. Wait for processing (the product states up to ~3 hours for account creation, and 24-48 hours for code activation). 3. Open the admin mailbox and locate the report email. 4. Compare its contents against the submitted job.</t>
+  </si>
+  <si>
+    <t>Admin mailbox &lt;MAIL_READABLE_ADMIN_ACCOUNT&gt;; the Request ID from step 1.</t>
+  </si>
+  <si>
+    <t>A report email reaches the admin mailbox naming the same Request ID and row count as the confirmation screen, and reporting the per-row outcomes. [ASSUMED]</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01: the other team repeat this step in five separate bulk cases (TC_STU_016, 017, 018, 019, 020) - "check if corresponding email is appearing in admin inbox and shows all the required details" - and we verify the email report nowhere. Fixture required before this can be automated: a mail-readable admin account. Scope that first; the case is written so it can be executed manually in the meantime. Written against the children path but applies to every async bulk job.</t>
+  </si>
+  <si>
+    <t>Blocked at design time (skill rule 4): no mail-readable admin fixture exists on thor. Unblock by provisioning an admin whose mailbox is programmatically readable, then re-scope the case across the five bulk flows.</t>
+  </si>
+  <si>
+    <t>TST_SBLK_TC_17</t>
+  </si>
+  <si>
+    <t>Verify the bulk CSV upload accepts 200 records and rejects 201</t>
+  </si>
+  <si>
+    <t>On the adult bulk-creation form with the CSV template downloaded.</t>
+  </si>
+  <si>
+    <t>1. Build a CSV of exactly 200 valid rows and upload it. 2. Note whether the grid populates and the submit count. 3. Build a CSV of 201 valid rows and upload it. 4. Read the resulting message.</t>
+  </si>
+  <si>
+    <t>Two generated CSVs in the real template format - 200 rows and 201 rows.</t>
+  </si>
+  <si>
+    <t>The 200-row file is accepted and the grid reports 200 rows. The 201-row file is rejected with a message naming the limit. [ASSUMED] - the exact rejection copy is not captured.</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_STU_016/017, whose expected results state the cap twice ("&lt;=200 records"). TST_SBLK_TC_12's Remarks already record that the adult CSV page enforces a 200-record maximum with its own wording - so the limit is known and the boundary case was simply missing. Boundary cases at a documented cap are the pattern that repeatedly caught real defects in the Classes work. Side-effect free if the 200-row file is never submitted. Generate the CSVs to the exact template headers.</t>
   </si>
 </sst>
 </file>
@@ -1725,7 +1941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -2127,7 +2343,7 @@
         <v>72</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>24</v>
@@ -2144,13 +2360,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>17</v>
@@ -2162,16 +2378,16 @@
         <v>19</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>24</v>
@@ -2188,13 +2404,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>48</v>
@@ -2206,16 +2422,16 @@
         <v>19</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>24</v>
@@ -2232,13 +2448,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>48</v>
@@ -2250,16 +2466,16 @@
         <v>19</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>24</v>
@@ -2276,13 +2492,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>17</v>
@@ -2294,16 +2510,16 @@
         <v>19</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>24</v>
@@ -2320,13 +2536,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>17</v>
@@ -2338,16 +2554,16 @@
         <v>19</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>24</v>
@@ -2364,13 +2580,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>17</v>
@@ -2382,25 +2598,25 @@
         <v>19</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2408,13 +2624,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>17</v>
@@ -2426,16 +2642,16 @@
         <v>19</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>24</v>
@@ -2452,13 +2668,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>17</v>
@@ -2470,16 +2686,16 @@
         <v>19</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>24</v>
@@ -2496,13 +2712,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>17</v>
@@ -2514,16 +2730,16 @@
         <v>19</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>24</v>
@@ -2540,13 +2756,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>48</v>
@@ -2558,16 +2774,16 @@
         <v>19</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>24</v>
@@ -2584,13 +2800,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>48</v>
@@ -2599,19 +2815,19 @@
         <v>55</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>24</v>
@@ -2628,13 +2844,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>17</v>
@@ -2646,16 +2862,16 @@
         <v>19</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>24</v>
@@ -2672,13 +2888,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>17</v>
@@ -2687,19 +2903,19 @@
         <v>41</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>24</v>
@@ -2716,13 +2932,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>17</v>
@@ -2731,19 +2947,19 @@
         <v>18</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>24</v>
@@ -2760,13 +2976,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>48</v>
@@ -2775,19 +2991,19 @@
         <v>41</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>24</v>
@@ -2804,13 +3020,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>48</v>
@@ -2822,13 +3038,13 @@
         <v>19</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>45</v>
@@ -2848,13 +3064,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>17</v>
@@ -2863,25 +3079,25 @@
         <v>41</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>24</v>
@@ -2892,13 +3108,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>17</v>
@@ -2910,22 +3126,22 @@
         <v>19</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>24</v>
@@ -2936,13 +3152,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>17</v>
@@ -2951,25 +3167,25 @@
         <v>41</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>24</v>
@@ -2980,13 +3196,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>17</v>
@@ -2995,16 +3211,16 @@
         <v>41</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>45</v>
@@ -3013,7 +3229,7 @@
         <v>24</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>24</v>
@@ -3024,13 +3240,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>48</v>
@@ -3039,25 +3255,25 @@
         <v>55</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>24</v>
@@ -3068,13 +3284,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>62</v>
@@ -3086,22 +3302,22 @@
         <v>19</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>24</v>
@@ -3112,13 +3328,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>17</v>
@@ -3130,22 +3346,22 @@
         <v>19</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>24</v>
@@ -3156,13 +3372,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>17</v>
@@ -3174,25 +3390,25 @@
         <v>19</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="34" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3200,13 +3416,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>17</v>
@@ -3215,25 +3431,25 @@
         <v>18</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>24</v>
@@ -3244,13 +3460,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>62</v>
@@ -3259,25 +3475,25 @@
         <v>18</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>24</v>
@@ -3288,13 +3504,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>17</v>
@@ -3303,25 +3519,25 @@
         <v>18</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>24</v>
@@ -3332,13 +3548,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>48</v>
@@ -3347,25 +3563,25 @@
         <v>41</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>24</v>
@@ -3376,13 +3592,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>48</v>
@@ -3391,25 +3607,25 @@
         <v>41</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>24</v>
@@ -3420,13 +3636,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>62</v>
@@ -3435,25 +3651,25 @@
         <v>41</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>24</v>
@@ -3464,13 +3680,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>17</v>
@@ -3482,22 +3698,22 @@
         <v>19</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>24</v>
@@ -3508,13 +3724,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>48</v>
@@ -3523,25 +3739,25 @@
         <v>41</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>24</v>
@@ -3552,13 +3768,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>62</v>
@@ -3567,25 +3783,25 @@
         <v>18</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>24</v>
@@ -3596,13 +3812,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>17</v>
@@ -3611,25 +3827,25 @@
         <v>18</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>24</v>
@@ -3640,13 +3856,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>62</v>
@@ -3655,25 +3871,25 @@
         <v>18</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>24</v>
@@ -3684,13 +3900,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>17</v>
@@ -3702,22 +3918,22 @@
         <v>19</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>24</v>
@@ -3728,13 +3944,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>48</v>
@@ -3743,28 +3959,28 @@
         <v>41</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3772,13 +3988,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>48</v>
@@ -3790,22 +4006,22 @@
         <v>19</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>24</v>
@@ -3816,13 +4032,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>62</v>
@@ -3831,25 +4047,25 @@
         <v>41</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>24</v>
@@ -3860,13 +4076,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>17</v>
@@ -3875,25 +4091,25 @@
         <v>18</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>24</v>
@@ -3904,13 +4120,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>48</v>
@@ -3922,22 +4138,22 @@
         <v>19</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>24</v>
@@ -3948,13 +4164,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>17</v>
@@ -3963,25 +4179,25 @@
         <v>18</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>24</v>
@@ -3992,13 +4208,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>17</v>
@@ -4007,25 +4223,25 @@
         <v>18</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>24</v>
@@ -4036,13 +4252,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>17</v>
@@ -4051,25 +4267,25 @@
         <v>18</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>24</v>
@@ -4080,13 +4296,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>17</v>
@@ -4095,25 +4311,25 @@
         <v>41</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>24</v>
@@ -4124,13 +4340,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>17</v>
@@ -4142,22 +4358,22 @@
         <v>19</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N55" s="2" t="s">
         <v>24</v>
@@ -4168,13 +4384,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>17</v>
@@ -4183,25 +4399,25 @@
         <v>41</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N56" s="2" t="s">
         <v>24</v>
@@ -4212,13 +4428,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>48</v>
@@ -4227,25 +4443,25 @@
         <v>41</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>24</v>
@@ -4256,13 +4472,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>62</v>
@@ -4271,25 +4487,25 @@
         <v>18</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>24</v>
@@ -4300,13 +4516,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>62</v>
@@ -4315,25 +4531,25 @@
         <v>41</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>24</v>
@@ -4344,13 +4560,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>62</v>
@@ -4359,27 +4575,423 @@
         <v>41</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N60" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="N69" s="2" t="s">
         <v>24</v>
       </c>
     </row>
